--- a/ig/ch-elm/ValueSet-ch-elm-results-sal-org-complete.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-sal-org-complete.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2040,7 +2040,7 @@
     <t>5595000</t>
   </si>
   <si>
-    <t>Salmonella Typhi (organism)</t>
+    <t>Salmonella Typhi</t>
   </si>
   <si>
     <t>398377009</t>

--- a/ig/ch-elm/ValueSet-ch-elm-results-sal-org-complete.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-sal-org-complete.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5445" uniqueCount="5443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5453" uniqueCount="5451">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2823,6 +2823,12 @@
     <t>Salmonella Athinai (organism)</t>
   </si>
   <si>
+    <t>23131001</t>
+  </si>
+  <si>
+    <t>Salmonella Ajiobo (organism)</t>
+  </si>
+  <si>
     <t>114382003</t>
   </si>
   <si>
@@ -3909,6 +3915,12 @@
     <t>Salmonella Masembe (organism)</t>
   </si>
   <si>
+    <t>62136003</t>
+  </si>
+  <si>
+    <t>Salmonella Dublin (organism)</t>
+  </si>
+  <si>
     <t>11903004</t>
   </si>
   <si>
@@ -8967,6 +8979,12 @@
     <t>Salmonella Osnabrueck (organism)</t>
   </si>
   <si>
+    <t>31564006</t>
+  </si>
+  <si>
+    <t>Salmonella Claibornei (organism)</t>
+  </si>
+  <si>
     <t>398481005</t>
   </si>
   <si>
@@ -10963,6 +10981,12 @@
   </si>
   <si>
     <t>Salmonella II 17:b:e,n,x,z15 (organism)</t>
+  </si>
+  <si>
+    <t>398559003</t>
+  </si>
+  <si>
+    <t>Salmonella group O:9 (organism)</t>
   </si>
   <si>
     <t>114465001</t>
@@ -16607,7 +16631,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B2708"/>
+  <dimension ref="A1:B2712"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -38267,15 +38291,47 @@
         <v>5440</v>
       </c>
       <c r="B2707" t="s" s="2">
-        <v>5440</v>
+        <v>5441</v>
       </c>
     </row>
     <row r="2708">
       <c r="A2708" t="s" s="2">
-        <v>5441</v>
+        <v>5442</v>
       </c>
       <c r="B2708" t="s" s="2">
-        <v>5442</v>
+        <v>5443</v>
+      </c>
+    </row>
+    <row r="2709">
+      <c r="A2709" t="s" s="2">
+        <v>5444</v>
+      </c>
+      <c r="B2709" t="s" s="2">
+        <v>5445</v>
+      </c>
+    </row>
+    <row r="2710">
+      <c r="A2710" t="s" s="2">
+        <v>5446</v>
+      </c>
+      <c r="B2710" t="s" s="2">
+        <v>5447</v>
+      </c>
+    </row>
+    <row r="2711">
+      <c r="A2711" t="s" s="2">
+        <v>5448</v>
+      </c>
+      <c r="B2711" t="s" s="2">
+        <v>5448</v>
+      </c>
+    </row>
+    <row r="2712">
+      <c r="A2712" t="s" s="2">
+        <v>5449</v>
+      </c>
+      <c r="B2712" t="s" s="2">
+        <v>5450</v>
       </c>
     </row>
   </sheetData>

--- a/ig/ch-elm/ValueSet-ch-elm-results-sal-org-complete.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-sal-org-complete.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/ValueSet-ch-elm-results-sal-org-complete.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-sal-org-complete.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
